--- a/packs/aerodrome/v2026/checklist.xlsx
+++ b/packs/aerodrome/v2026/checklist.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,6 +512,11 @@
           <t>Dual</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>SubChecklist</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -544,7 +549,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>1</t>
@@ -555,24 +559,31 @@
           <t>ขั้นเตรียมการ &amp; ยื่นคำขอ</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>แจ้งความประสงค์ (Expression of Interest) ต่อ กพท. พร้อมประเมินการปฏิบัติการบินเบื้องต้น</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Doc 9774 §; ASC/กพท.</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+          <t>Doc 9774 §; ASC/กพท. · EASA ADR.OR.B (application)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>ตรวจหลักฐานการติดต่อ กพท. ก่อนยื่นคำขอ และผลประเมินเบื้องต้น — สนามบินส่วนบุคคล (ไม่เปิดสาธารณะ) อยู่นอกขอบเขต EASA ใช้กฎ กพท./พ.ร.บ.เดินอากาศเป็นหลัก EASA ใช้เทียบเป็น best practice</t>
+        </is>
+      </c>
       <c r="Q2" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>มีหนังสือ/อีเมลแจ้งความประสงค์ถึง กพท. พร้อมวันที่
+ระบุประเภทสนามบิน (ส่วนบุคคล) และวัตถุประสงค์ชัดเจน
+มีบันทึกการหารือ/คำแนะนำจาก กพท. (ถ้ามี)</t>
         </is>
       </c>
     </row>
@@ -607,7 +618,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>1</t>
@@ -618,24 +628,32 @@
           <t>ขั้นเตรียมการ &amp; ยื่นคำขอ</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>ประเมิน flight operations: ระยะห่างสนามบิน/สนามบินทหารใกล้เคียง, สิ่งกีดขวาง/ภูมิประเทศ, ห้วงอากาศควบคุม, instrument procedure ที่มี</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Annex 14; Doc 9774</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ทบทวนรายงานประเมินการปฏิบัติการบิน: ต้องระบุข้อมูลจริงพร้อมแผนที่/พิกัด ไม่ใช่คำบรรยายลอย ๆ</t>
+        </is>
+      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ระยะห่างสนามบิน/เฮลิพอร์ตข้างเคียง + สนามบินทหาร ระบุเป็นตัวเลข
+แผนที่สิ่งกีดขวางและภูมิประเทศรอบแนวขึ้น-ลง
+โครงสร้างห้วงอากาศ/เส้นทางบินที่เกี่ยวข้อง
+ผลกระทบต่อ traffic pattern ของสนามบินข้างเคียง</t>
         </is>
       </c>
     </row>
@@ -670,7 +688,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>1</t>
@@ -681,24 +698,30 @@
           <t>ขั้นเตรียมการ &amp; ยื่นคำขอ</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>ยืนยันว่าที่ตั้งไม่กระทบความปลอดภัยการบิน จึงเดินหน้าคำขอต่อได้</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Doc 9774 §3</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>ดูข้อสรุปของผู้ประเมิน: มีลายเซ็น/วันที่ และเงื่อนไขแนบท้าย (ถ้ามี)</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ข้อสรุป 'เดินหน้าต่อได้' เป็นลายลักษณ์อักษร
+เงื่อนไข/ข้อจำกัดที่ต้องปฏิบัติระบุครบ</t>
         </is>
       </c>
     </row>
@@ -733,7 +756,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>1</t>
@@ -744,24 +766,32 @@
           <t>ขั้นเตรียมการ &amp; ยื่นคำขอ</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>ยื่นคำขออย่างเป็นทางการ พร้อมเอกสารตามที่กำหนด + คู่มือสนามบิน (Aerodrome Manual)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Annex 14; TCAR/กพท.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
+          <t>Annex 14; TCAR/กพท. · EASA ADR.OR.B.015</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>ตรวจชุดคำขอ: แบบฟอร์ม กพท. + เอกสารแนบครบตามรายการ + คู่มือสนามบินฉบับยื่น</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>แบบคำขอกรอกครบ ลงนามโดยผู้มีอำนาจ
+คู่มือสนามบิน (Aerodrome Manual) ฉบับยื่นแนบครบ
+หลักฐานสิทธิในที่ดิน/ผังบริเวณแนบ
+หลักฐานชำระค่าธรรมเนียม (ถ้ามี)</t>
         </is>
       </c>
     </row>
@@ -796,7 +826,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>2</t>
@@ -807,21 +836,21 @@
           <t>ขั้นประเมินโดยผู้ตรวจ</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>ผู้ตรวจ (Aerodrome Inspector) ทบทวน flight operations assessment</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Doc 9774</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>จำลองมุมมองผู้ตรวจ กพท.: ประเด็นที่ผู้ตรวจจะถาม มีคำตอบ/หลักฐานพร้อมหรือไม่</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>N</t>
@@ -859,7 +888,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>2</t>
@@ -870,24 +898,31 @@
           <t>ขั้นประเมินโดยผู้ตรวจ</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>จัดทำ/ทบทวน aeronautical study (ถ้ามีประเด็นเบี่ยงเบนจากมาตรฐาน)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Annex 14</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>ถ้ามีข้อเบี่ยงเบนจากมาตรฐาน (เช่น strip แคบกว่าเกณฑ์) ต้องมี aeronautical study รองรับพร้อมมาตรการชดเชย</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>รายการข้อเบี่ยงเบนทั้งหมดถูกชี้บ่ง
+แต่ละข้อมี study/การประเมินความเสี่ยง + มาตรการชดเชย
+ผู้มีอำนาจลงนามรับรองผล</t>
         </is>
       </c>
     </row>
@@ -922,7 +957,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>2</t>
@@ -933,21 +967,21 @@
           <t>ขั้นประเมินโดยผู้ตรวจ</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>ประเมินคู่มือสนามบินที่ยื่น (ดูแท็บ 2)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Annex 14 App; Doc 9774</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+          <t>Annex 14 App; Doc 9774 · EASA ADR.OR.E.005</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ใช้แท็บ Part 2 ตรวจทีละหัวข้อ — คู่มือต้องตรงกับสภาพจริงหน้างาน</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>N</t>
@@ -985,7 +1019,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>2</t>
@@ -996,21 +1029,21 @@
           <t>ขั้นประเมินโดยผู้ตรวจ</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>การตรวจหน้างาน (Site Visit) — ตรวจสิ่งอำนวยความสะดวก/อุปกรณ์ (ดูแท็บ 3)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Doc 9774; Annex 14</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>ใช้แท็บ Part 3 ตรวจหน้างานทีละรายการ พร้อมถ่ายรูปหลักฐานแนบในแอป</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>N</t>
@@ -1048,7 +1081,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>3</t>
@@ -1059,24 +1091,30 @@
           <t>ขั้นออกใบรับรอง &amp; ประกาศ</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>กพท. ออกหรือปฏิเสธใบรับรอง / กำหนดเงื่อนไข-ข้อจำกัดการใช้งาน</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Doc 9774 §</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>ทบทวนร่างเงื่อนไข/ข้อจำกัดที่คาดว่าจะได้รับ และผู้รับผิดชอบปฏิบัติตามแต่ละเงื่อนไข</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>รายการเงื่อนไขที่คาดว่าจะกำหนด + ผู้รับผิดชอบ
+ช่องทางติดตามสถานะคำขอกับ กพท.</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1149,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>3</t>
@@ -1122,24 +1159,30 @@
           <t>ขั้นออกใบรับรอง &amp; ประกาศ</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>ประกาศสถานะสนามบินและข้อมูลที่กำหนดใน AIP</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Annex 15 / AIS</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>ตรวจว่าข้อมูลสนามบินที่จะประกาศ (หรือสถานะไม่ประกาศสำหรับสนามบินส่วนบุคคล) ถูกต้องตรงกับข้อเท็จจริง</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ข้อมูล ARP/elevation/runway ตรงกับผลสำรวจ
+ช่องทางการแจ้งผู้ใช้สนามบิน (ถ้าไม่เข้า AIP)</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1217,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>3</t>
@@ -1185,24 +1227,31 @@
           <t>ขั้นออกใบรับรอง &amp; ประกาศ</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>จัดทำระบบแจ้งการเปลี่ยนแปลง (change process) ที่ต้อง/ไม่ต้องขออนุมัติก่อน</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>OTAR139/Annex14</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+          <t>OTAR139/Annex14 · EASA ADR.OR.B.040</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>ดูขั้นตอนเป็นลายลักษณ์อักษร: การเปลี่ยนแปลงแบบไหนต้องขออนุมัติ กพท. ก่อน แบบไหนแค่แจ้ง</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>ตารางจำแนกประเภทการเปลี่ยนแปลง (prior approval / notify)
+แบบฟอร์ม/ช่องทางแจ้ง กพท.
+ผู้รับผิดชอบอนุมัติภายใน</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1286,6 @@
           <t>ขั้นตอนการรับรองสนามบิน (Doc 9774)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>3</t>
@@ -1248,21 +1296,21 @@
           <t>ขั้นออกใบรับรอง &amp; ประกาศ</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>บันทึกรอบการตรวจติดตาม (continuing surveillance) หลังได้ใบรับรอง</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Doc 9774</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+          <t>Doc 9774 · EASA ADR.OR.C</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>ดูปฏิทินรอบตรวจติดตามของ กพท. หลังได้ใบรับรอง และการเตรียมความพร้อมรับตรวจประจำปี</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>N</t>
@@ -1300,7 +1348,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>1</t>
@@ -1311,24 +1358,32 @@
           <t>Part 1 — ทั่วไป (General)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>วัตถุประสงค์และขอบเขตของคู่มือ; ระบบควบคุมฉบับ/การแก้ไข (version control)</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+          <t>Annex 14 App · EASA ADR.OR.E.005</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>เปิดคู่มือหน้าแรก ๆ: ต้องมีวัตถุประสงค์ ขอบเขต และระบบควบคุมเอกสาร</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>หน้า amendment record / LEP
+เลขฉบับ/วันที่มีผลบังคับ
+ผู้ถือสำเนา (distribution list)
+ลายเซ็นอนุมัติคู่มือ</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1418,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>1</t>
@@ -1374,24 +1428,31 @@
           <t>Part 1 — ทั่วไป (General)</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>เงื่อนไขการใช้สนามบิน (conditions of use) — ประเภท/ขนาดอากาศยานที่อนุญาต, ส่วนบุคคลเท่านั้น</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>ตรวจข้อความ conditions of use: ต้องเขียนชัดว่า 'ส่วนบุคคล — ใช้เฉพาะผู้ได้รับอนุญาต'</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ประเภท/น้ำหนักอากาศยานสูงสุดที่รับได้
+VFR เท่านั้น หรือเงื่อนไขกลางคืน/IMC
+ขั้นตอนขออนุญาตใช้สนามบิน (PPR)</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1487,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>1</t>
@@ -1437,21 +1497,21 @@
           <t>Part 1 — ทั่วไป (General)</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>ระบบการให้ข้อมูลข่าวสารการบิน (AIS) ที่มีอยู่</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>ดูวิธีที่นักบินผู้ใช้สนามบินได้รับข้อมูลปัจจุบัน (เช่น เอกสารข้อมูลสนามบิน, ไลน์กลุ่ม, NOTAM ผ่าน กพท.)</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>N</t>
@@ -1489,7 +1549,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>1</t>
@@ -1500,24 +1559,30 @@
           <t>Part 1 — ทั่วไป (General)</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>ระบบบันทึกการเคลื่อนไหวอากาศยาน (aircraft movement records)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>สุ่มดูบันทึกการใช้สนามบินย้อนหลัง: มีวันที่ ทะเบียน เที่ยว ขึ้น-ลง ครบ</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>สมุด/ระบบบันทึกเที่ยวบินเป็นปัจจุบัน
+สถิติจำนวนเที่ยวบิน/เดือน สรุปได้</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1617,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>1</t>
@@ -1563,21 +1627,21 @@
           <t>Part 1 — ทั่วไป (General)</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>หน้าที่ความรับผิดชอบของผู้ดำเนินการสนามบิน (obligations of operator)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+          <t>Annex 14 App · EASA ADR.OR.C.005</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ตรวจว่าหน้าที่ผู้ดำเนินการเขียนครบ: ดูแลความปลอดภัย รายงานเหตุ ปฏิบัติตามเงื่อนไขใบรับรอง</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>N</t>
@@ -1615,7 +1679,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>2</t>
@@ -1626,24 +1689,31 @@
           <t>Part 2 — ข้อมูลที่ตั้งสนามบิน (Site)</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>แผนผังแสดงขอบเขตสนามบิน (site plan / boundaries)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>เทียบแผนผังกับภาพถ่ายดาวเทียม/หน้างานจริง — ขอบเขตต้องตรง</t>
+        </is>
+      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>แสดง runway/taxiway/apron/อาคาร ครบ
+มาตราส่วนและทิศเหนือ
+ขอบเขตที่ดินตรงโฉนด/เอกสารสิทธิ</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1748,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>2</t>
@@ -1689,21 +1758,21 @@
           <t>Part 2 — ข้อมูลที่ตั้งสนามบิน (Site)</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>ระยะห่างจากเมือง/ชุมชนที่ใกล้ที่สุด และสิ่งอำนวยความสะดวกหลัก</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>ตรวจตัวเลขระยะทาง/ทิศทางไปชุมชน โรงพยาบาล สถานีดับเพลิงที่ใกล้ที่สุด (ใช้ในแผนฉุกเฉินด้วย)</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>N</t>
@@ -1741,7 +1810,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>2</t>
@@ -1752,24 +1820,30 @@
           <t>Part 2 — ข้อมูลที่ตั้งสนามบิน (Site)</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>หลักฐานกรรมสิทธิ์/สิทธิใช้ที่ดิน (title / ownership / สิทธิครอบครอง)</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>ตรวจเอกสารสิทธิตัวจริง/สำเนา: ชื่อผู้ถือกรรมสิทธิ์สัมพันธ์กับผู้ขอใบรับรอง (เจ้าของเอง/สัญญาเช่าระยะยาว)</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>โฉนด/น.ส.4 หรือสัญญาเช่า + ระยะเวลา
+ครอบคลุมพื้นที่ strip/RESA ทั้งหมด ไม่เฉพาะ runway</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1878,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>3</t>
@@ -1815,24 +1888,31 @@
           <t>Part 3 — ข้อมูลที่ต้องรายงานต่อ AIS</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>ข้อมูลทั่วไป: ชื่อสนามบิน, ที่ตั้ง, ARP, elevation, reference temperature, datum</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Annex 14 App / Annex 15</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>เทียบข้อมูลในคู่มือกับผลสำรวจจริง (survey report): พิกัด ARP, elevation, temperature อ้างอิง</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>ผลสำรวจโดยผู้สำรวจ/วิธีที่เชื่อถือได้
+datum ที่ใช้ (WGS-84)
+วันที่สำรวจไม่เก่าเกินไป</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1947,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>3</t>
@@ -1878,24 +1957,31 @@
           <t>Part 3 — ข้อมูลที่ต้องรายงานต่อ AIS</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>มิติทางวิ่งและข้อมูล: runway, strip, RESA, taxiway, apron, declared distances (TORA/TODA/ASDA/LDA)</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+          <t>Annex 14 App · EASA CS ADR-DSN</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>ตรวจตาราง declared distances ทุกทิศทางวิ่ง และการวัดจริงหน้างานสอดคล้อง</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>TORA/TODA/ASDA/LDA ครบทั้ง 2 ทิศ
+ตัวเลข strip/RESA ตรงกับหน้างาน
+ความกว้าง runway/taxiway/apron ระบุครบ</t>
         </is>
       </c>
     </row>
@@ -1930,7 +2016,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>3</t>
@@ -1941,24 +2026,31 @@
           <t>Part 3 — ข้อมูลที่ต้องรายงานต่อ AIS</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>Obstacle Limitation Surfaces (OLS) และสิ่งกีดขวางที่สำรวจได้</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.4</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+          <t>Annex 14 Ch.4 · EASA CS ADR-DSN Ch.H/J</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>ดูแผนผัง OLS + ทะเบียนสิ่งกีดขวาง: ต้องสำรวจจริง ไม่ใช่ประมาณ</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>แผนผัง OLS (approach/transitional/inner horizontal ฯลฯ)
+ทะเบียนสิ่งกีดขวางพร้อมความสูง/พิกัด
+สิ่งกีดขวางที่ทะลุ surface มีการประเมิน/study</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2085,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>3</t>
@@ -2004,21 +2095,21 @@
           <t>Part 3 — ข้อมูลที่ต้องรายงานต่อ AIS</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>เครื่องช่วยการเดินอากาศด้วยตา (visual aids), marking, lighting, signs</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.5</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+          <t>Annex 14 Ch.5 · EASA CS ADR-DSN</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>เทียบรายการ marking/lighting/signs ในคู่มือกับของจริง (จะยืนยันอีกครั้งใน Part 3)</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>N</t>
@@ -2056,7 +2147,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
           <t>4</t>
@@ -2067,21 +2157,21 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>ขั้นตอนรายงานข้อมูลต่อ AIS / NOTAM</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Doc 9981</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>ดูขั้นตอน: ใครมีอำนาจขอ NOTAM, ช่องทางติดต่อ, ตัวอย่าง NOTAM ที่เคยออก (ถ้ามี)</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>N</t>
@@ -2119,7 +2209,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>4</t>
@@ -2130,24 +2219,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>การควบคุมการเข้าออกเขตปฏิบัติการ (movement area access control)</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>ตรวจขั้นตอนควบคุมการเข้าเขตปฏิบัติการ: รั้ว/ประตู/ผู้มีสิทธิเข้า</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>รายชื่อ/ประเภทผู้มีสิทธิเข้า airside
+วิธีควบคุมบุคคลภายนอก/escort
+ป้ายเตือนเขตหวงห้าม</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2278,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>4</t>
@@ -2193,24 +2288,33 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>แผนฉุกเฉินสนามบิน (Aerodrome Emergency Plan)</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.9</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+          <t>Annex 14 Ch.9 · EASA ADR.OPS.B.005</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>ตรวจแผนฉุกเฉิน: ต้องใช้ได้จริงกับทรัพยากรของสนามบินส่วนบุคคล ไม่ลอกแบบสนามบินใหญ่</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>ประเภทเหตุที่ครอบคลุม (อากาศยานอุบัติเหตุ/ไฟไหม้/พยาบาล)
+ผังการแจ้งเหตุ + เบอร์โทรปัจจุบัน
+หน่วยงานภายนอก (รพ./ดับเพลิง/ตำรวจ) + ระยะเวลาถึง
+แผนที่จุดรวมพล/เส้นทางเข้าฉุกเฉิน
+กำหนดซ้อมและบันทึกการซ้อมล่าสุด</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2349,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>4</t>
@@ -2256,24 +2359,32 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>การดับเพลิงและกู้ภัย (RFF) — ระดับตามประเภทสนามบิน</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.9</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+          <t>Annex 14 Ch.9 · EASA ADR.OPS.B.010</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>ตรวจการกำหนดระดับ RFF ตามอากาศยานใหญ่สุดที่ใช้ และอุปกรณ์จริงต้องมีตามนั้น</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>กำหนด RFF category ไว้ชัดเจน
+ถังดับเพลิง/สารดับเพลิงชนิดและปริมาณตามเกณฑ์
+ผู้รับผิดชอบผ่านการฝึกดับเพลิงอากาศยาน
+การตรวจอุปกรณ์ประจำเดือนมีบันทึก</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2419,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>4</t>
@@ -2319,24 +2429,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>การตรวจสภาพเขตปฏิบัติการและ OLS เป็นประจำ (inspections)</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Annex 14 App / Doc 9981</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+          <t>Annex 14 App / Doc 9981 · EASA ADR.OPS.B.015</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>ดูแบบฟอร์ม daily/weekly inspection และบันทึกจริงย้อนหลัง — ไม่ใช่มีแค่แบบฟอร์มเปล่า</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>แบบฟอร์มตรวจประจำวัน/สัปดาห์
+บันทึกย้อนหลังต่อเนื่อง มีลายเซ็น
+ขั้นตอนเมื่อพบข้อบกพร่อง (ปิดใช้/แจ้งซ่อม/NOTAM)</t>
         </is>
       </c>
     </row>
@@ -2371,7 +2488,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>4</t>
@@ -2382,24 +2498,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>การบำรุงรักษาเขตปฏิบัติการ, visual aids, ระบบไฟฟ้า</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+          <t>Annex 14 App · EASA ADR.OPS.C</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>ตรวจแผนบำรุงรักษา: ผิวทาง หญ้า ระบบระบายน้ำ ไฟ เครื่องหมาย</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ตารางบำรุงรักษาราย เดือน/ไตรมาส/ปี
+บันทึกงานที่ทำแล้ว
+ผู้รับผิดชอบแต่ละงาน</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2557,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
           <t>4</t>
@@ -2445,21 +2567,21 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>การจัดการความปลอดภัยงานก่อสร้าง/บำรุงรักษาในเขตปฏิบัติการ (works safety)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>Doc 9981</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>ดูขั้นตอนความปลอดภัยงานก่อสร้าง/ซ่อมในเขตปฏิบัติการ: การปิดพื้นที่ แจ้งผู้ใช้ ป้าย/เครื่องหมายชั่วคราว</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>N</t>
@@ -2497,7 +2619,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>4</t>
@@ -2508,24 +2629,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>การจัดการลานจอด (apron management) และความปลอดภัยลานจอด</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>ตรวจการจัดระเบียบลานจอด: ตำแหน่งจอด เส้นทางขับ ผู้ควบคุม</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>ผังตำแหน่งจอด + ระยะห่างปีก
+ขั้นตอน start-up/taxi ในลานจอด
+การควบคุม FOD ในลานจอด</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2688,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
           <t>4</t>
@@ -2571,24 +2698,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>การควบคุมยานพาหนะในเขตปฏิบัติการ (vehicle control)</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+          <t>Annex 14 App · EASA ADR.OPS.B.025</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>ตรวจกติกายานพาหนะใน airside: ผู้มีสิทธิขับ เส้นทาง ความเร็ว การให้ทางอากาศยาน</t>
+        </is>
+      </c>
       <c r="Q34" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>รายชื่อผู้ได้รับอนุญาตขับใน airside
+กฎให้ทางอากาศยานเสมอ
+อุปกรณ์รถ: ธง/ไฟ/วิทยุ</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2757,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
           <t>4</t>
@@ -2634,24 +2767,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>การจัดการอันตรายจากสัตว์/นก (wildlife hazard management)</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.9</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
+          <t>Annex 14 Ch.9 · EASA ADR.OPS.B.020</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>ตรวจการจัดการนก/สัตว์: บันทึกการพบ วิธีไล่ การลดสิ่งดึงดูด (น้ำขัง ขยะ พืชผล)</t>
+        </is>
+      </c>
       <c r="Q35" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>บันทึก wildlife sighting/strike
+อุปกรณ์/วิธีไล่ที่ใช้ได้จริง
+มาตรการลดแหล่งอาหาร-น้ำรอบสนาม</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2826,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
           <t>4</t>
@@ -2697,21 +2836,21 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>การควบคุมสิ่งกีดขวาง (obstacle control) รอบสนามบิน</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>Annex 14 Ch.4</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>ดูขั้นตอนเฝ้าระวังสิ่งกีดขวางใหม่รอบสนาม (ต้นไม้โต สิ่งปลูกสร้างใหม่ เครน) และช่องทางประสานเจ้าของพื้นที่</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>N</t>
@@ -2749,7 +2888,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>4</t>
@@ -2760,21 +2898,21 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>การเคลื่อนย้ายอากาศยานที่ใช้การไม่ได้ (disabled aircraft removal)</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>ตรวจแผนเคลื่อนย้ายอากาศยานเสีย/อุบัติเหตุพ้นทางวิ่ง: ใครทำ ใช้อุปกรณ์อะไร ประสานใคร</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr">
         <is>
           <t>N</t>
@@ -2812,7 +2950,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>4</t>
@@ -2823,24 +2960,31 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>การจัดการวัตถุอันตราย / การเติมเชื้อเพลิง (fuel handling)</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+          <t>Annex 14 App · EASA ADR.OPS (fuel)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>ตรวจขั้นตอนเชื้อเพลิง: การเก็บ การเติม การควบคุมคุณภาพ และความปลอดภัยอัคคีภัย</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>จุดเก็บเชื้อเพลิงมีป้าย/กันไฟ/ระบายอากาศ
+ขั้นตอนเติม: ดับเครื่อง ต่อสายดิน ถังดับเพลิงพร้อม
+การตรวจคุณภาพ/น้ำปนในเชื้อเพลิง + บันทึก</t>
         </is>
       </c>
     </row>
@@ -2875,7 +3019,6 @@
           <t>เอกสารและคู่มือสนามบิน</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>4</t>
@@ -2886,24 +3029,30 @@
           <t>Part 4 — ขั้นตอนปฏิบัติการ &amp; มาตรการความปลอดภัย</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>ระบบการจัดการความปลอดภัย (Safety Management System - SMS)</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Annex 19 / Annex 14 App</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+          <t>Annex 19 / Annex 14 App · EASA ADR.OR.D.005</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>ตรวจว่า SMS ย่อส่วนเหมาะกับขนาดสนามบิน แต่ครบ 4 องค์ประกอบ (policy/risk/assurance/promotion)</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>เอกสาร SMS ฉบับปัจจุบัน
+สอดคล้องกับ SMS ของ D-0507 (ถ้าเชื่อมกัน) โดยไม่สับสนบทบาท</t>
         </is>
       </c>
     </row>
@@ -2938,7 +3087,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>1</t>
@@ -2949,24 +3097,32 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>ทางวิ่ง (Runway) — มิติ, สภาพผิว, ความลาด</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.3</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
+          <t>Annex 14 Ch.3 · EASA CS ADR-DSN.B</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>เดินตรวจ runway ตลอดความยาว: วัดจริงเทียบคู่มือ ดูสภาพผิว รอยแตก หลุม น้ำขัง</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>ความกว้าง-ยาวตรงกับ declared
+ผิวเรียบ ไม่มีหลุม/รอยแตกอันตราย
+ความลาดตามเกณฑ์ ไม่มีแอ่งน้ำขัง
+ไม่มี FOD/หญ้ารุกผิวทาง</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3157,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>1</t>
@@ -3012,21 +3167,21 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>ไหล่ทางวิ่ง (Runway shoulders)</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.3</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+          <t>Annex 14 Ch.3 · EASA CS ADR-DSN.B</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>ตรวจไหล่ทาง: ความกว้าง ความแข็งแรง รอยต่อกับผิวทางเรียบเสมอกัน</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr">
         <is>
           <t>N</t>
@@ -3064,7 +3219,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>1</t>
@@ -3075,24 +3229,31 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>พื้นที่ปลอดภัยข้างทางวิ่ง (Runway strip)</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.3</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+          <t>Annex 14 Ch.3 · EASA CS ADR-DSN.B</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>เดินตรวจ strip เต็มแนว: ปรับระดับ ไม่มีวัตถุอันตราย สิ่งติดตั้งที่จำเป็นต้อง frangible</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>ความกว้าง strip ตามประกาศ
+ไม่มีคู น้ำขัง วัตถุแข็งในเขต graded
+อุปกรณ์ในเขต strip เป็นแบบแตกหักง่าย (frangible)</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3288,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>1</t>
@@ -3138,21 +3298,21 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>พื้นที่ปลอดภัยปลายทางวิ่ง (RESA)</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.3</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+          <t>Annex 14 Ch.3 · EASA CS ADR-DSN.B</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>ตรวจ RESA ทั้งสองปลาย: ขนาด สภาพพื้นผิวรองรับอากาศยานวิ่งเลยได้โดยไม่เสียหายรุนแรง</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>N</t>
@@ -3190,7 +3350,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>1</t>
@@ -3201,21 +3360,21 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>Stopway / Clearway (ถ้ามี)</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>Annex 14 Ch.3</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>ถ้าประกาศไว้ต้องตรวจตามเกณฑ์ ถ้าไม่มี ให้ N.A พร้อมระบุเหตุผลในช่อง comment</t>
+        </is>
+      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>N</t>
@@ -3253,7 +3412,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
           <t>1</t>
@@ -3264,21 +3422,21 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>ทางขับ (Taxiway) + ไหล่ + strip</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.3</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
+          <t>Annex 14 Ch.3 · EASA CS ADR-DSN.D</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>ตรวจ taxiway: ความกว้าง ผิว ไหล่ทาง ระยะห่างจากสิ่งกีดขวาง</t>
+        </is>
+      </c>
       <c r="Q45" t="inlineStr">
         <is>
           <t>N</t>
@@ -3316,7 +3474,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>1</t>
@@ -3327,21 +3484,21 @@
           <t>มิติและสภาพผิว (Dimensions &amp; Surface)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>ลานจอด (Apron)</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
           <t>Annex 14 Ch.3</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>ตรวจ apron: ขนาดพอกับจำนวนอากาศยาน ผิวแข็งแรง ความลาดระบายน้ำ ไม่ส่งผลให้อากาศยานไหล</t>
+        </is>
+      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>N</t>
@@ -3379,7 +3536,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>2</t>
@@ -3390,24 +3546,31 @@
           <t>สิ่งกีดขวาง (Obstacles)</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>การมีสิ่งกีดขวางภายใน Obstacle Limitation Surfaces (OLS)</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.4</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
+          <t>Annex 14 Ch.4 · EASA CS ADR-DSN Ch.H/J</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>ดูแผนผัง OLS + ทะเบียนสิ่งกีดขวาง: ต้องสำรวจจริง ไม่ใช่ประมาณ</t>
+        </is>
+      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>แผนผัง OLS (approach/transitional/inner horizontal ฯลฯ)
+ทะเบียนสิ่งกีดขวางพร้อมความสูง/พิกัด
+สิ่งกีดขวางที่ทะลุ surface มีการประเมิน/study</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3605,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>2</t>
@@ -3453,21 +3615,21 @@
           <t>สิ่งกีดขวาง (Obstacles)</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>ไฟที่อาจรบกวน/เป็นอันตรายต่อความปลอดภัยการบิน</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>Annex 14 Ch.5</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>สำรวจตอนพลบค่ำถ้าทำได้: ไฟภายนอกรอบสนามที่แยงตา/ทำให้สับสนกับไฟสนามบิน</t>
+        </is>
+      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>N</t>
@@ -3505,7 +3667,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
           <t>3</t>
@@ -3516,24 +3677,31 @@
           <t>ไฟสนามบิน (Aeronautical Ground Lighting) + บันทึก flight check</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>ไฟทางวิ่งและทางขับ (runway &amp; taxiway lighting)</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.5</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
+          <t>Annex 14 Ch.5 · EASA CS ADR-DSN.M</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ถ้าใช้กลางคืน: ทดสอบเปิดไฟจริง ดูครบดวง สี ระยะ ถ้าไม่ใช้กลางคืน → N.A + ระบุในช่อง comment</t>
+        </is>
+      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>ไฟขอบทางวิ่งครบ ไม่มีดวงดับ
+สี/ระยะห่างตามเกณฑ์
+ไฟ threshold/end ถูกต้อง</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3736,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>3</t>
@@ -3579,21 +3746,21 @@
           <t>ไฟสนามบิน (Aeronautical Ground Lighting) + บันทึก flight check</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>ไฟนำร่อน (approach lights) ถ้ามี</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
           <t>Annex 14 Ch.5</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>มีเฉพาะบางสนาม — ถ้าไม่มี ให้ N.A + เหตุผล (สนามบิน VFR กลางวัน)</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>N</t>
@@ -3631,7 +3798,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>3</t>
@@ -3642,21 +3808,21 @@
           <t>ไฟสนามบิน (Aeronautical Ground Lighting) + บันทึก flight check</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>PAPI / APAPI</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.5</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+          <t>Annex 14 Ch.5 · EASA CS ADR-DSN.M</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>ถ้าติดตั้ง: ทดสอบมุมร่อนด้วยการบิน/เครื่องมือ และมีบันทึกสอบเทียบ ถ้าไม่มี → N.A</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>N</t>
@@ -3694,7 +3860,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
           <t>3</t>
@@ -3705,21 +3870,21 @@
           <t>ไฟสนามบิน (Aeronautical Ground Lighting) + บันทึก flight check</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>ไฟส่องลานจอด (apron floodlighting)</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>Annex 14 Ch.5</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>ถ้าปฏิบัติการกลางคืน: ตรวจความสว่างพอ ไม่แยงตานักบิน ถ้าไม่ → N.A</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>N</t>
@@ -3757,7 +3922,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>3</t>
@@ -3768,21 +3932,21 @@
           <t>ไฟสนามบิน (Aeronautical Ground Lighting) + บันทึก flight check</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>ไฟสิ่งกีดขวาง (obstacle lighting)</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.6</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+          <t>Annex 14 Ch.6 · EASA CS ADR-DSN.Q</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>ตรวจไฟสิ่งกีดขวางบนวัตถุที่กำหนด: ติดจริง ทำงานกลางคืน มีระบบตรวจสอบดวงเสีย</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>N</t>
@@ -3820,7 +3984,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>3</t>
@@ -3831,21 +3994,21 @@
           <t>ไฟสนามบิน (Aeronautical Ground Lighting) + บันทึก flight check</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>ไฟที่นักบินเปิดเอง (pilot-activated lighting) ถ้ามี</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>Annex 14 Ch.5</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>ถ้ามี: ทดสอบการเปิดผ่านความถี่วิทยุจริง + ระยะเวลาไฟติด ถ้าไม่มี → N.A</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>N</t>
@@ -3883,7 +4046,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>4</t>
@@ -3894,21 +4056,21 @@
           <t>ระบบสนับสนุน (Support Systems)</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>ไฟฟ้าสำรอง (standby power)</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.8</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+          <t>Annex 14 Ch.8 · EASA CS ADR-DSN.S</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>ถ้าปฏิบัติการกลางคืน/มีไฟสนามบิน: ทดสอบไฟสำรองทำงานจริง เวลาสลับ ถ้าไม่จำเป็น → N.A + เหตุผล</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>N</t>
@@ -3946,7 +4108,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>4</t>
@@ -3957,24 +4118,31 @@
           <t>ระบบสนับสนุน (Support Systems)</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>ตัวชี้ทิศทางลม (wind direction indicator) และไฟส่อง</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.5</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+          <t>Annex 14 Ch.5 · EASA CS ADR-DSN.K</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>ตรวจถุงลม: ตำแหน่งเห็นชัดจากอากาศ สภาพผ้าไม่ซีด/ขาด หมุนอิสระ ไฟส่อง (ถ้าใช้กลางคืน)</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>เห็นได้จากทุกทิศ approach
+สีตัดกับพื้นหลัง สภาพดี
+วงกลมพื้นขาว (ถ้ากำหนด)</t>
         </is>
       </c>
     </row>
@@ -4009,7 +4177,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>4</t>
@@ -4020,24 +4187,31 @@
           <t>ระบบสนับสนุน (Support Systems)</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>เครื่องหมายและ marker ในเขตปฏิบัติการ (markings &amp; markers)</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.5</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+          <t>Annex 14 Ch.5 · EASA CS ADR-DSN.L</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>เดินตรวจเครื่องหมาย: designation, centre line, threshold ชัดเจนไม่ซีด</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>runway designation ถูกต้องตามทิศแม่เหล็กปัจจุบัน
+เส้น centre line/threshold ชัด
+marker ขอบเขต (ถ้าทางวิ่งหญ้า) ครบ</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4246,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>4</t>
@@ -4083,21 +4256,21 @@
           <t>ระบบสนับสนุน (Support Systems)</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>ป้ายในเขตปฏิบัติการ (signs)</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>Annex 14 Ch.5</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>ตรวจป้าย (ถ้ามี): อ่านชัด ตำแหน่งถูก แตกหักง่าย — สนามเล็กอาจไม่มีป้าย ให้ N.A + เหตุผล</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>N</t>
@@ -4135,7 +4308,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>4</t>
@@ -4146,21 +4318,21 @@
           <t>ระบบสนับสนุน (Support Systems)</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>จุดยึดอากาศยาน (tie-down) และจุดต่อสายดิน (earthing) ถ้ามี</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
           <t>Annex 14 Ch.3</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>ตรวจจุดยึดอากาศยาน: แข็งแรง ครบตามจำนวนจุดจอด + จุดต่อสายดินใช้ได้จริง</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>N</t>
@@ -4198,7 +4370,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>5</t>
@@ -4209,24 +4380,32 @@
           <t>อุปกรณ์ปฏิบัติการ &amp; ความปลอดภัย</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>อุปกรณ์และการติดตั้งดับเพลิง-กู้ภัย (RFF equipment &amp; installations)</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.9</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+          <t>Annex 14 Ch.9 · EASA ADR.OPS.B.010</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>ตรวจการกำหนดระดับ RFF ตามอากาศยานใหญ่สุดที่ใช้ และอุปกรณ์จริงต้องมีตามนั้น</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>กำหนด RFF category ไว้ชัดเจน
+ถังดับเพลิง/สารดับเพลิงชนิดและปริมาณตามเกณฑ์
+ผู้รับผิดชอบผ่านการฝึกดับเพลิงอากาศยาน
+การตรวจอุปกรณ์ประจำเดือนมีบันทึก</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4440,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>5</t>
@@ -4272,21 +4450,21 @@
           <t>อุปกรณ์ปฏิบัติการ &amp; ความปลอดภัย</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
           <t>อุปกรณ์บำรุงรักษาเขตปฏิบัติการ (รวม friction measurement ถ้ามี)</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
           <t>Annex 14 Ch.10</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>ตรวจเครื่องมือที่ใช้ดูแลสนามจริง: เครื่องตัดหญ้า อุปกรณ์ซ่อมผิว เครื่องมือวัด</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>N</t>
@@ -4324,7 +4502,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>5</t>
@@ -4335,21 +4512,21 @@
           <t>อุปกรณ์ปฏิบัติการ &amp; ความปลอดภัย</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
           <t>อุปกรณ์เคลื่อนย้ายอากาศยานที่ใช้การไม่ได้ (disabled aircraft removal)</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>Annex 14 Ch.9</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>ตรวจแผนเคลื่อนย้ายอากาศยานเสีย/อุบัติเหตุพ้นทางวิ่ง: ใครทำ ใช้อุปกรณ์อะไร ประสานใคร</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>N</t>
@@ -4387,7 +4564,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
           <t>5</t>
@@ -4398,21 +4574,21 @@
           <t>อุปกรณ์ปฏิบัติการ &amp; ความปลอดภัย</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
           <t>ขั้นตอน + อุปกรณ์จัดการสัตว์อันตราย (wildlife management)</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
           <t>Annex 14 Ch.9</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>ตรวจอุปกรณ์ไล่สัตว์ที่มีจริง (ประทัด/เสียง/ธง) และผู้รับผิดชอบรู้วิธีใช้</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>N</t>
@@ -4450,7 +4626,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
           <t>5</t>
@@ -4461,21 +4636,21 @@
           <t>อุปกรณ์ปฏิบัติการ &amp; ความปลอดภัย</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
           <t>วิทยุสื่อสารสองทางในรถของผู้ดำเนินการสนามบินในเขตปฏิบัติการ</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
           <t>Annex 14 Ch.9</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>ทดสอบวิทยุในรถ/มือถือที่ใช้ใน airside: ติดต่อความถี่สนามบินได้จริง แบตเตอรี่/ชาร์จพร้อม</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>N</t>
@@ -4513,7 +4688,6 @@
           <t>ตรวจกายภาพหน้างาน</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>5</t>
@@ -4524,24 +4698,32 @@
           <t>อุปกรณ์ปฏิบัติการ &amp; ความปลอดภัย</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
           <t>สิ่งอำนวยความสะดวกด้านเชื้อเพลิง (fuelling facilities) และความปลอดภัย</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
           <t>Annex 14 App</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>ตรวจจุดเติมเชื้อเพลิงหน้างาน: ถังเก็บ สภาพสายและหัวจ่าย สายดิน ป้ายห้ามสูบบุหรี่ ถังดับเพลิงประจำจุด</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>ถังเก็บมี bund/กันรั่วซึม
+สายดิน + คลิปหนีบใช้ได้
+ถังดับเพลิงประจำจุดเติม ไม่หมดอายุ
+บันทึกตรวจน้ำปน/คุณภาพประจำ</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4758,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
           <t>1</t>
@@ -4587,24 +4768,31 @@
           <t>โครงสร้างองค์กรและผู้รับผิดชอบ (Accountability)</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
           <t>Accountable Manager — เป็นบุคคลของ SPI ชัดเจน มีอำนาจและงบประมาณ</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
           <t>Annex 19; EASA ADR.OR.D.015</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>สัมภาษณ์ + ดูเอกสารแต่งตั้ง: AM ต้องเป็นคนของ SPI มีอำนาจสั่งการและงบประมาณจริง</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>หนังสือแต่งตั้ง AM ลงนามครบ
+AM อธิบายหน้าที่ความรับผิดชอบของตนได้
+มีอำนาจอนุมัติงบด้านความปลอดภัย</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4827,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
           <t>1</t>
@@ -4650,24 +4837,31 @@
           <t>โครงสร้างองค์กรและผู้รับผิดชอบ (Accountability)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
           <t>ผังองค์กรขั้นต่ำ: Airside/Ops, SMS, การบำรุงรักษาสิ่งอำนวยความสะดวก</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
           <t>Doc 9774; EASA ADR.OR.D</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>ตรวจผังองค์กร: ทุกกล่องมีชื่อคนจริง ไม่มีตำแหน่งว่างในงานความปลอดภัยหลัก</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ผังเป็นปัจจุบัน ระบุชื่อ-ตำแหน่ง
+งาน Airside/SMS/Maintenance มีผู้รับผิดชอบครบ
+คนเดียวควบหลายหน้าที่ → มีการประเมินว่าไม่ขัดกัน</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4896,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
           <t>1</t>
@@ -4713,21 +4906,21 @@
           <t>โครงสร้างองค์กรและผู้รับผิดชอบ (Accountability)</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
           <t>Post-holder ที่ D-0507 เข้าไปเสริม มีนิติสัมพันธ์กับผู้ถือใบอนุญาต (จ้าง/secondment/แต่งตั้งเป็นลายลักษณ์อักษร)</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
           <t>Doc 9774</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>ตรวจเอกสารนิติสัมพันธ์ของบุคลากร D-0507 ที่ไปช่วยงานสนามบิน: จ้าง/secondment/แต่งตั้ง ต้องเป็นลายลักษณ์อักษร</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>N</t>
@@ -4765,7 +4958,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>1</t>
@@ -4776,24 +4968,31 @@
           <t>โครงสร้างองค์กรและผู้รับผิดชอบ (Accountability)</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
           <t>สัญญา/MOU ระหว่าง SPI–D-0507 ระบุขอบเขตบริการสนับสนุนชัดเจน</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>อ่านสัญญา/MOU: ขอบเขตบริการ ความรับผิดชอบ และการสิ้นสุดสัญญาชัดเจน</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>ระบุขอบเขตงานสนับสนุนเป็นข้อ ๆ
+ระบุว่า SPI คงความรับผิดชอบตามใบรับรอง
+ลงนามสองฝ่าย + วันที่</t>
         </is>
       </c>
     </row>
@@ -4828,7 +5027,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
           <t>1</t>
@@ -4839,21 +5037,21 @@
           <t>โครงสร้างองค์กรและผู้รับผิดชอบ (Accountability)</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
           <t>ความรับผิดชอบตามใบอนุญาตอยู่ที่ SPI (ไม่ทำให้เข้าใจว่า D-0507 เป็นผู้ดำเนินการ)</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>Doc 9774</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>ตรวจเอกสารทั้งหมดไม่มีข้อความที่ทำให้เข้าใจว่า D-0507 เป็นผู้ดำเนินการสนามบิน</t>
+        </is>
+      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>N</t>
@@ -4891,7 +5089,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
           <t>2</t>
@@ -4902,24 +5099,31 @@
           <t>คุณสมบัติและการฝึกอบรมบุคลากร</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>บุคลากรที่ปฏิบัติงานในเขตปฏิบัติการมีคุณสมบัติ/ผ่านการฝึก (competency &amp; training records)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>Annex 14 App; EASA ADR.OR.D.017</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>สุ่มแฟ้มบุคลากร airside: การฝึกที่กำหนด ทำจริง มีบันทึก</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>รายการฝึกบังคับต่อบทบาท (airside safety, RFF, วิทยุ)
+บันทึกการฝึกรายคน เป็นปัจจุบัน
+การประเมินความสามารถ (competency check)</t>
         </is>
       </c>
     </row>
@@ -4954,7 +5158,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr">
         <is>
           <t>2</t>
@@ -4965,21 +5168,21 @@
           <t>คุณสมบัติและการฝึกอบรมบุคลากร</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
           <t>โปรแกรมฝึกอบรมและบันทึกการฝึก (training programme &amp; records)</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
           <t>EASA ADR.OR.D.017</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>ดูแผนฝึกประจำปี + recurrent training: ไม่ใช่ฝึกครั้งเดียวตอนเริ่มงาน</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>N</t>
@@ -5017,7 +5220,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
           <t>2</t>
@@ -5028,21 +5230,21 @@
           <t>คุณสมบัติและการฝึกอบรมบุคลากร</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>การควบคุมผู้รับเหมา/ผู้ให้บริการภายนอก (contracted activities oversight)</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
           <t>EASA ADR.OR.D.010</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>ตรวจการกำกับผู้รับเหมา (ตัดหญ้า/ซ่อมผิว/เชื้อเพลิง): briefing ก่อนเข้า escort และเงื่อนไขความปลอดภัยในสัญญา</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>N</t>
@@ -5080,7 +5282,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
           <t>3</t>
@@ -5091,21 +5292,21 @@
           <t>ระบบการจัดการความปลอดภัย (SMS)</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>นโยบายและวัตถุประสงค์ด้านความปลอดภัย (safety policy &amp; objectives)</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
           <t>Annex 19</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>อ่าน safety policy: ลงนามโดย AM คนปัจจุบัน สื่อสารให้ทีมรู้จริง (ถามพนักงานได้)</t>
+        </is>
+      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>N</t>
@@ -5143,7 +5344,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
           <t>3</t>
@@ -5154,24 +5354,31 @@
           <t>ระบบการจัดการความปลอดภัย (SMS)</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>การชี้บ่งอันตรายและการประเมิน-จัดการความเสี่ยง (hazard ID &amp; risk management)</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
           <t>Annex 19</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>ดูทะเบียนความเสี่ยง (hazard log): มีรายการจริงของสนามนี้ ประเมินและมีมาตรการ ไม่ใช่แบบฟอร์มเปล่า</t>
+        </is>
+      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>hazard log มีรายการปัจจุบัน
+การประเมินความเสี่ยง (likelihood/severity)
+มาตรการควบคุม + ผู้รับผิดชอบ + ติดตามผล</t>
         </is>
       </c>
     </row>
@@ -5206,7 +5413,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
           <t>3</t>
@@ -5217,24 +5423,31 @@
           <t>ระบบการจัดการความปลอดภัย (SMS)</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>การประกันความปลอดภัย (safety assurance) — รายงานเหตุ, ตรวจสอบภายใน</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr">
         <is>
           <t>Annex 19</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>ตรวจระบบรายงานเหตุ/เหตุเกือบเกิด + การตรวจสอบภายใน: มีช่องทาง มีตัวอย่างรายงานจริง</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>ช่องทางรายงานที่ทุกคนเข้าถึง
+บันทึกเหตุ/near-miss ที่ผ่านมา + การจัดการ
+แผนตรวจสอบภายใน + ผลครั้งล่าสุด</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5482,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
           <t>3</t>
@@ -5280,21 +5492,21 @@
           <t>ระบบการจัดการความปลอดภัย (SMS)</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
           <t>การส่งเสริมความปลอดภัย (safety promotion &amp; training)</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
           <t>Annex 19</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>ดูหลักฐานกิจกรรม: safety briefing, บอร์ดประชาสัมพันธ์, การแบ่งปันบทเรียน</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>N</t>
@@ -5332,7 +5544,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
           <t>3</t>
@@ -5343,24 +5554,31 @@
           <t>ระบบการจัดการความปลอดภัย (SMS)</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>แผนฉุกเฉินสนามบินและการซ้อม (emergency plan &amp; exercises)</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Annex 14 Ch.9</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+          <t>Annex 14 Ch.9 · EASA ADR.OPS.B.005</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>ตรวจบันทึกการซ้อมแผนฉุกเฉินครั้งล่าสุด: วันที่ ผู้ร่วม บทเรียนที่ได้ และการแก้ไขแผนตามบทเรียน</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>N</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>ซ้อมภายในรอบเวลาที่กำหนด
+รายงานผลการซ้อม + lessons learned
+ปรับแผนตามบทเรียนแล้ว</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5613,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
           <t>4</t>
@@ -5406,21 +5623,21 @@
           <t>ความพร้อมวันตรวจ (Inspection-day readiness)</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
           <t>มอบหมายบทบาททีมรับตรวจ: Lead/SPOC, Doc Controller, Airside, Ops/Safety, Escort, Scribe</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
           <t>แนวปฏิบัติ</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>ดูรายชื่อทีมรับตรวจ: ทุกบทบาทมีตัวจริงและรู้หน้าที่ (ถามได้)</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>N</t>
@@ -5458,7 +5675,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>4</t>
@@ -5469,21 +5685,21 @@
           <t>ความพร้อมวันตรวจ (Inspection-day readiness)</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>ซ้อมตรวจภายใน (mock inspection) + เดินเส้นทางตรวจ</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
           <t>แนวปฏิบัติ</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>ตรวจบันทึก mock inspection: ทำจริง มี finding และปิดก่อนวันตรวจ</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>N</t>
@@ -5521,7 +5737,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>4</t>
@@ -5532,21 +5747,21 @@
           <t>ความพร้อมวันตรวจ (Inspection-day readiness)</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>ปิด corrective action ที่ค้างทั้งหมดก่อนวันตรวจ</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>แนวปฏิบัติ</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>ดูทะเบียน CAR/CAP ของการเตรียมรับรอง: ทุกข้อปิดหรือมีแผนชัดก่อนวันตรวจ</t>
+        </is>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>N</t>
@@ -5584,7 +5799,6 @@
           <t>องค์กร บุคลากร และ SMS</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
           <t>4</t>
@@ -5595,21 +5809,21 @@
           <t>ความพร้อมวันตรวจ (Inspection-day readiness)</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
           <t>เตรียม entry/exit meeting + เอกสาร index ค้นได้เร็ว</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>แนวปฏิบัติ</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>ตรวจความพร้อมเอกสารวันตรวจ: วาระ entry meeting, index เอกสารหาได้ใน 2 นาที, ห้อง/ผู้จด</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>N</t>
